--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -454,23 +454,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>16.59369</v>
+        <v>17.15288</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58102</v>
+        <v>16.7393</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45119</v>
+        <v>16.836</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52547</v>
+        <v>42.9824</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05199</v>
+        <v>0.05072</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82374</v>
+        <v>1.86272</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.12134</v>
+        <v>17.13411</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86485</v>
+        <v>16.56054</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7494</v>
+        <v>16.65167</v>
       </c>
       <c r="F3" t="n">
-        <v>42.72516</v>
+        <v>42.7067</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05084</v>
+        <v>0.0523</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84337</v>
+        <v>1.84583</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.24103</v>
+        <v>17.27244</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57378</v>
+        <v>16.62974</v>
       </c>
       <c r="E4" t="n">
-        <v>17.45295</v>
+        <v>16.85565</v>
       </c>
       <c r="F4" t="n">
-        <v>42.18824</v>
+        <v>42.29734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05195</v>
+        <v>0.05168</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85311</v>
+        <v>1.84955</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.81977</v>
+        <v>17.10897</v>
       </c>
       <c r="D5" t="n">
-        <v>16.70543</v>
+        <v>16.96419</v>
       </c>
       <c r="E5" t="n">
-        <v>16.70417</v>
+        <v>17.076</v>
       </c>
       <c r="F5" t="n">
-        <v>42.51353</v>
+        <v>42.81178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05137</v>
+        <v>0.05218</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83686</v>
+        <v>1.85472</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8315</v>
+        <v>16.98214</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3221</v>
+        <v>16.68856</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76945</v>
+        <v>16.87525</v>
       </c>
       <c r="F6" t="n">
-        <v>41.82986</v>
+        <v>44.07982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05144</v>
+        <v>0.05064</v>
       </c>
       <c r="H6" t="n">
-        <v>1.889</v>
+        <v>1.84142</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.24034</v>
+        <v>17.34374</v>
       </c>
       <c r="D7" t="n">
-        <v>16.74821</v>
+        <v>16.93335</v>
       </c>
       <c r="E7" t="n">
-        <v>17.17321</v>
+        <v>17.03773</v>
       </c>
       <c r="F7" t="n">
-        <v>43.28172</v>
+        <v>43.41032</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0511</v>
+        <v>0.05119</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83658</v>
+        <v>1.84837</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.48266</v>
+        <v>17.09145</v>
       </c>
       <c r="D8" t="n">
-        <v>17.1025</v>
+        <v>16.61822</v>
       </c>
       <c r="E8" t="n">
-        <v>17.07159</v>
+        <v>17.05827</v>
       </c>
       <c r="F8" t="n">
-        <v>42.73544</v>
+        <v>43.06792</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05043</v>
+        <v>0.0514</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89007</v>
+        <v>1.84286</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.09124</v>
+        <v>17.15461</v>
       </c>
       <c r="D9" t="n">
-        <v>16.7344</v>
+        <v>16.8003</v>
       </c>
       <c r="E9" t="n">
-        <v>16.42967</v>
+        <v>17.02215</v>
       </c>
       <c r="F9" t="n">
-        <v>42.94078</v>
+        <v>42.48974</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05144</v>
+        <v>0.051</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83714</v>
+        <v>1.8439</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.02814</v>
+        <v>17.12701</v>
       </c>
       <c r="D10" t="n">
-        <v>16.43394</v>
+        <v>16.57976</v>
       </c>
       <c r="E10" t="n">
-        <v>16.82427</v>
+        <v>16.80695</v>
       </c>
       <c r="F10" t="n">
-        <v>42.24541</v>
+        <v>42.93376</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05075</v>
+        <v>0.05156</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84228</v>
+        <v>1.82025</v>
       </c>
     </row>
     <row r="11">
@@ -691,17 +696,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -713,26 +713,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>17.05124</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16.62912</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.1181</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.02177</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05109</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.82553</v>
+          <t>Trace 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -741,24 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>16.8692</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.69802</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.80498</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43.0004</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05086</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.85897</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,24 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>16.62359</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.49295</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.02007</v>
-      </c>
-      <c r="F14" t="n">
-        <v>43.4172</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05232</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.82979</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -791,24 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>17.02242</v>
-      </c>
-      <c r="D15" t="n">
-        <v>17.00225</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.682</v>
-      </c>
-      <c r="F15" t="n">
-        <v>43.49547</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05093</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.83607</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -816,24 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>16.55027</v>
-      </c>
-      <c r="D16" t="n">
-        <v>17.01738</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.91163</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.20262</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.84892</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -841,24 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>16.97323</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.80328</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.91539</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43.4438</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05073</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.82766</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -866,24 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>16.72825</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.62548</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.02471</v>
-      </c>
-      <c r="F18" t="n">
-        <v>43.10805</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05311</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.80176</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -891,24 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.79031</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.90522</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.14464</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.54472</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05215</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.8061</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -916,24 +772,6 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>16.96171</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.9634</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.72159</v>
-      </c>
-      <c r="F20" t="n">
-        <v>43.33893</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.04985</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.86324</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -989,28 +827,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.77886</v>
+        <v>0.76341</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08196000000000001</v>
+        <v>0.08136</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6242</v>
+        <v>0.61748</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95965</v>
+        <v>0.96717</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10891</v>
+        <v>0.11232</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00781</v>
+        <v>0.00764</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09264</v>
+        <v>0.09558</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12803</v>
+        <v>0.12794</v>
       </c>
     </row>
     <row r="23">
@@ -1020,28 +858,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.73976</v>
+        <v>0.75549</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08119</v>
+        <v>0.08243</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60433</v>
+        <v>0.61805</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99976</v>
+        <v>0.96772</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1106</v>
+        <v>0.11299</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00764</v>
+        <v>0.00761</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09608999999999999</v>
+        <v>0.09361</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12736</v>
+        <v>0.12928</v>
       </c>
     </row>
     <row r="24">
@@ -1051,28 +889,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7532799999999999</v>
+        <v>0.7543299999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08328000000000001</v>
+        <v>0.08273999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61359</v>
+        <v>0.61982</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97181</v>
+        <v>0.97041</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11176</v>
+        <v>0.11055</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0076</v>
+        <v>0.00779</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09576999999999999</v>
+        <v>0.09264</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12774</v>
+        <v>0.1274</v>
       </c>
     </row>
     <row r="25">
@@ -1082,28 +920,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76103</v>
+        <v>0.75835</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08149000000000001</v>
+        <v>0.08183</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60756</v>
+        <v>0.62248</v>
       </c>
       <c r="F25" t="n">
-        <v>0.98336</v>
+        <v>0.96019</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10852</v>
+        <v>0.11007</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00771</v>
+        <v>0.0075</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09519</v>
+        <v>0.09438000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12706</v>
+        <v>0.12814</v>
       </c>
     </row>
     <row r="26">
@@ -1113,28 +951,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.76771</v>
+        <v>0.76183</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08282</v>
+        <v>0.08241</v>
       </c>
       <c r="E26" t="n">
-        <v>0.61808</v>
+        <v>0.6144500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97953</v>
+        <v>0.96896</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11085</v>
+        <v>0.11153</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0076</v>
+        <v>0.00762</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09468</v>
+        <v>0.09446</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12976</v>
+        <v>0.12832</v>
       </c>
     </row>
     <row r="27">
@@ -1144,28 +982,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7529400000000001</v>
+        <v>0.75826</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08309</v>
+        <v>0.08159</v>
       </c>
       <c r="E27" t="n">
-        <v>0.61844</v>
+        <v>0.6046899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.97428</v>
+        <v>0.98443</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10931</v>
+        <v>0.11065</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00768</v>
+        <v>0.00757</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09412</v>
+        <v>0.09351</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12711</v>
+        <v>0.12916</v>
       </c>
     </row>
     <row r="28">
@@ -1175,28 +1013,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76188</v>
+        <v>0.7478399999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08311</v>
+        <v>0.08222</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61066</v>
+        <v>0.61338</v>
       </c>
       <c r="F28" t="n">
-        <v>0.97473</v>
+        <v>0.9764</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1111</v>
+        <v>0.10951</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00768</v>
+        <v>0.00766</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09544999999999999</v>
+        <v>0.09311999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12994</v>
+        <v>0.12849</v>
       </c>
     </row>
     <row r="29">
@@ -1206,28 +1044,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76711</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08328000000000001</v>
+        <v>0.08314000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60109</v>
+        <v>0.61805</v>
       </c>
       <c r="F29" t="n">
-        <v>0.97151</v>
+        <v>0.97558</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1097</v>
+        <v>0.10989</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00776</v>
+        <v>0.00767</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09648</v>
+        <v>0.09381</v>
       </c>
       <c r="J29" t="n">
-        <v>0.13236</v>
+        <v>0.12996</v>
       </c>
     </row>
     <row r="30">
@@ -1237,28 +1075,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74785</v>
+        <v>0.74556</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08180999999999999</v>
+        <v>0.08089</v>
       </c>
       <c r="E30" t="n">
-        <v>0.62451</v>
+        <v>0.62085</v>
       </c>
       <c r="F30" t="n">
-        <v>0.98749</v>
+        <v>0.96384</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10944</v>
+        <v>0.11109</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00758</v>
+        <v>0.00773</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09332</v>
+        <v>0.09490999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12621</v>
+        <v>0.12844</v>
       </c>
     </row>
   </sheetData>
